--- a/public/exports-with-coowners/29189897.xlsx
+++ b/public/exports-with-coowners/29189897.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -22789,7 +22789,7 @@
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t xml:space="preserve">311769950</t>
+          <t xml:space="preserve">311769954</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">

--- a/public/exports-with-coowners/29189897.xlsx
+++ b/public/exports-with-coowners/29189897.xlsx
@@ -22789,7 +22789,7 @@
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t xml:space="preserve">311769954</t>
+          <t xml:space="preserve">311769950</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
@@ -22939,7 +22939,7 @@
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t xml:space="preserve">311769950</t>
+          <t xml:space="preserve">311769953</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -24739,7 +24739,7 @@
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t xml:space="preserve">311824278</t>
+          <t xml:space="preserve">311824283</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">

--- a/public/exports-with-coowners/29189897.xlsx
+++ b/public/exports-with-coowners/29189897.xlsx
@@ -22939,7 +22939,7 @@
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t xml:space="preserve">311769953</t>
+          <t xml:space="preserve">311769950</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -23291,7 +23291,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændkjærgade 92</t>
+          <t xml:space="preserve">Mosevej 37</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -23301,30 +23301,30 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t xml:space="preserve">7841251</t>
+          <t xml:space="preserve">5023541</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J311">
-        <v>1613</v>
+        <v>1328</v>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t xml:space="preserve">311781557</t>
+          <t xml:space="preserve">311787606</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">EnergiOptimo ApS</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-30</t>
+          <t xml:space="preserve">2034-09-26</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -23351,12 +23351,12 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kolding Kommune</t>
+          <t xml:space="preserve">OMJ Ejendomme, Kolding ApS</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -23366,7 +23366,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændkjærgade 92</t>
+          <t xml:space="preserve">Toldbodgade 10</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
@@ -23376,30 +23376,30 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t xml:space="preserve">7841251</t>
+          <t xml:space="preserve">328041, 328044, 328045, 328046, 328047</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J312">
-        <v>486</v>
+        <v>5696</v>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t xml:space="preserve">311781557</t>
+          <t xml:space="preserve">311800098</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Elmlund Erhverv v/Carsten E Rasmussen</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-30</t>
+          <t xml:space="preserve">2034-11-28</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -23426,12 +23426,12 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kolding Kommune</t>
+          <t xml:space="preserve">ARBEJDERNES ANDELSBOLIGFORENING</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -23441,7 +23441,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændkjærgade 92</t>
+          <t xml:space="preserve">Ny Vestergade 2</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
@@ -23451,30 +23451,30 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t xml:space="preserve">7841251</t>
+          <t xml:space="preserve">327203, 327204, 327205, 327206, 327207</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J313">
-        <v>540</v>
+        <v>3246</v>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t xml:space="preserve">311781557</t>
+          <t xml:space="preserve">311802497</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-30</t>
+          <t xml:space="preserve">2034-12-13</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -23516,40 +23516,40 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændkjærgade 92</t>
+          <t xml:space="preserve">Hjarupvej 14</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t xml:space="preserve">6000</t>
+          <t xml:space="preserve">6640</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t xml:space="preserve">7841251</t>
+          <t xml:space="preserve">5027423</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J314">
-        <v>428</v>
+        <v>4461</v>
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t xml:space="preserve">311781557</t>
+          <t xml:space="preserve">311818310</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-30</t>
+          <t xml:space="preserve">2035-03-18</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -23591,7 +23591,7 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændkjærgade 92</t>
+          <t xml:space="preserve">W. Kiørboes Vej 3</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
@@ -23601,30 +23601,30 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t xml:space="preserve">7841251</t>
+          <t xml:space="preserve">7524697</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J315">
-        <v>2260</v>
+        <v>825</v>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t xml:space="preserve">311781557</t>
+          <t xml:space="preserve">311820661</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-30</t>
+          <t xml:space="preserve">2035-03-27</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -23666,40 +23666,40 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændkjærgade 92</t>
+          <t xml:space="preserve">Vesterled 1</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t xml:space="preserve">6000</t>
+          <t xml:space="preserve">6580</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">7841251</t>
+          <t xml:space="preserve">7110241</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J316">
-        <v>1303</v>
+        <v>742</v>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t xml:space="preserve">311781557</t>
+          <t xml:space="preserve">311824146</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-30</t>
+          <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -23741,40 +23741,40 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændkjærgade 92</t>
+          <t xml:space="preserve">Ødis Byvej 6</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t xml:space="preserve">6000</t>
+          <t xml:space="preserve">6580</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">7841251</t>
+          <t xml:space="preserve">7110241</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J317">
-        <v>253</v>
+        <v>542</v>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t xml:space="preserve">311781557</t>
+          <t xml:space="preserve">311823954</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-30</t>
+          <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -23816,40 +23816,40 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændkjærgade 92</t>
+          <t xml:space="preserve">Ødis Byvej 6</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t xml:space="preserve">6000</t>
+          <t xml:space="preserve">6580</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">7841251</t>
+          <t xml:space="preserve">7110241</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J318">
-        <v>562</v>
+        <v>1337</v>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t xml:space="preserve">311781557</t>
+          <t xml:space="preserve">311824146</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-30</t>
+          <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -23891,7 +23891,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændkjærgade 92</t>
+          <t xml:space="preserve">Esbjergvej 108</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -23901,30 +23901,30 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">7841251</t>
+          <t xml:space="preserve">4387067</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J319">
-        <v>505</v>
+        <v>320</v>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t xml:space="preserve">311781557</t>
+          <t xml:space="preserve">311824278</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-30</t>
+          <t xml:space="preserve">2035-04-10</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -23966,7 +23966,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændkjærgade 92</t>
+          <t xml:space="preserve">Skovvejen 1A</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
@@ -23976,30 +23976,30 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">7841251</t>
+          <t xml:space="preserve">5681097</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J320">
-        <v>380</v>
+        <v>982</v>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t xml:space="preserve">311781557</t>
+          <t xml:space="preserve">311826209</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-30</t>
+          <t xml:space="preserve">2035-04-22</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -24041,7 +24041,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dannersvej 4</t>
+          <t xml:space="preserve">Skovvejen 1B</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -24051,30 +24051,30 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">7841251</t>
+          <t xml:space="preserve">5681097</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J321">
-        <v>2917</v>
+        <v>1766</v>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t xml:space="preserve">311781557</t>
+          <t xml:space="preserve">311826212</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-30</t>
+          <t xml:space="preserve">2035-04-22</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -24116,40 +24116,40 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mosevej 37</t>
+          <t xml:space="preserve">Herredsvej 45</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t xml:space="preserve">6000</t>
+          <t xml:space="preserve">6580</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">5023541</t>
+          <t xml:space="preserve">9071031</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J322">
-        <v>1328</v>
+        <v>2848</v>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t xml:space="preserve">311787606</t>
+          <t xml:space="preserve">311826636</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiOptimo ApS</t>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-26</t>
+          <t xml:space="preserve">2035-04-23</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -24176,12 +24176,12 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t xml:space="preserve">OMJ Ejendomme, Kolding ApS</t>
+          <t xml:space="preserve">Kolding Kommune</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -24191,40 +24191,40 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toldbodgade 10</t>
+          <t xml:space="preserve">Herredsvej 45</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t xml:space="preserve">6000</t>
+          <t xml:space="preserve">6580</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">328041, 328044, 328045, 328046, 328047</t>
+          <t xml:space="preserve">9071031</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J323">
-        <v>5696</v>
+        <v>1172</v>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800098</t>
+          <t xml:space="preserve">311826644</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmlund Erhverv v/Carsten E Rasmussen</t>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-11-28</t>
+          <t xml:space="preserve">2035-04-23</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -24251,12 +24251,12 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARBEJDERNES ANDELSBOLIGFORENING</t>
+          <t xml:space="preserve">Kolding Kommune</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -24266,40 +24266,40 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ny Vestergade 2</t>
+          <t xml:space="preserve">Herredsvej 45</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t xml:space="preserve">6000</t>
+          <t xml:space="preserve">6580</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t xml:space="preserve">327203, 327204, 327205, 327206, 327207</t>
+          <t xml:space="preserve">9071031</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J324">
-        <v>3246</v>
+        <v>2017</v>
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t xml:space="preserve">311802497</t>
+          <t xml:space="preserve">311826644</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-13</t>
+          <t xml:space="preserve">2035-04-23</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -24341,30 +24341,30 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjarupvej 14</t>
+          <t xml:space="preserve">Herredsvej 45</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t xml:space="preserve">6640</t>
+          <t xml:space="preserve">6580</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">5027423</t>
+          <t xml:space="preserve">9071031</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J325">
-        <v>4461</v>
+        <v>803</v>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t xml:space="preserve">311818310</t>
+          <t xml:space="preserve">311826644</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-18</t>
+          <t xml:space="preserve">2035-04-23</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -24416,40 +24416,40 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t xml:space="preserve">W. Kiørboes Vej 3</t>
+          <t xml:space="preserve">Herredsvej 45B</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t xml:space="preserve">6000</t>
+          <t xml:space="preserve">6580</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">7524697</t>
+          <t xml:space="preserve">9071031</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J326">
-        <v>825</v>
+        <v>371</v>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t xml:space="preserve">311820661</t>
+          <t xml:space="preserve">311826639</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-27</t>
+          <t xml:space="preserve">2035-04-23</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -24491,30 +24491,30 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterled 1</t>
+          <t xml:space="preserve">Sjølund Gade 28</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t xml:space="preserve">6580</t>
+          <t xml:space="preserve">6093</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">7110241</t>
+          <t xml:space="preserve">5069465</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J327">
-        <v>742</v>
+        <v>1387</v>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t xml:space="preserve">311824146</t>
+          <t xml:space="preserve">311827156</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
@@ -24524,7 +24524,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-09</t>
+          <t xml:space="preserve">2035-04-25</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -24566,30 +24566,30 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ødis Byvej 6</t>
+          <t xml:space="preserve">Hjarupvej 10</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t xml:space="preserve">6580</t>
+          <t xml:space="preserve">6000</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t xml:space="preserve">7110241</t>
+          <t xml:space="preserve">5069995</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J328">
-        <v>542</v>
+        <v>5886</v>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823954</t>
+          <t xml:space="preserve">311828899</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
@@ -24599,7 +24599,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-09</t>
+          <t xml:space="preserve">2035-05-02</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -24641,30 +24641,30 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ødis Byvej 6</t>
+          <t xml:space="preserve">Birkevej 9A</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t xml:space="preserve">6580</t>
+          <t xml:space="preserve">6070</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t xml:space="preserve">7110241</t>
+          <t xml:space="preserve">5170804</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J329">
-        <v>1337</v>
+        <v>361</v>
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t xml:space="preserve">311824146</t>
+          <t xml:space="preserve">311832714</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
@@ -24674,7 +24674,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-09</t>
+          <t xml:space="preserve">2035-05-19</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -24716,30 +24716,30 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Esbjergvej 108</t>
+          <t xml:space="preserve">Birkevej 9A</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t xml:space="preserve">6000</t>
+          <t xml:space="preserve">6070</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t xml:space="preserve">4387067</t>
+          <t xml:space="preserve">5170804</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J330">
-        <v>320</v>
+        <v>525</v>
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t xml:space="preserve">311824283</t>
+          <t xml:space="preserve">311832714</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
@@ -24749,7 +24749,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-10</t>
+          <t xml:space="preserve">2035-05-19</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -24791,7 +24791,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvejen 1A</t>
+          <t xml:space="preserve">Ågade 27</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
@@ -24801,20 +24801,20 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t xml:space="preserve">5681097</t>
+          <t xml:space="preserve">9218207</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J331">
-        <v>982</v>
+        <v>5961</v>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t xml:space="preserve">311826209</t>
+          <t xml:space="preserve">311832620</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
@@ -24824,7 +24824,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-22</t>
+          <t xml:space="preserve">2035-05-19</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -24866,17 +24866,17 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvejen 1B</t>
+          <t xml:space="preserve">Idrætsvej 1A</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t xml:space="preserve">6000</t>
+          <t xml:space="preserve">6580</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t xml:space="preserve">5681097</t>
+          <t xml:space="preserve">5028587</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -24885,11 +24885,11 @@
         </is>
       </c>
       <c r="J332">
-        <v>1766</v>
+        <v>3079</v>
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t xml:space="preserve">311826212</t>
+          <t xml:space="preserve">311833037</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
@@ -24899,7 +24899,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-22</t>
+          <t xml:space="preserve">2035-05-20</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -24941,30 +24941,30 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herredsvej 45</t>
+          <t xml:space="preserve">Rytterskolevej 15</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t xml:space="preserve">6580</t>
+          <t xml:space="preserve">6000</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t xml:space="preserve">9071031</t>
+          <t xml:space="preserve">10170544</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J333">
-        <v>2848</v>
+        <v>636</v>
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t xml:space="preserve">311826636</t>
+          <t xml:space="preserve">311834137</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
@@ -24974,7 +24974,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-23</t>
+          <t xml:space="preserve">2035-05-25</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -25016,30 +25016,30 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herredsvej 45</t>
+          <t xml:space="preserve">Seestvej 10</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t xml:space="preserve">6580</t>
+          <t xml:space="preserve">6000</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t xml:space="preserve">9071031</t>
+          <t xml:space="preserve">100068900</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J334">
-        <v>1172</v>
+        <v>1983</v>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t xml:space="preserve">311826644</t>
+          <t xml:space="preserve">311837586</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
@@ -25049,7 +25049,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-23</t>
+          <t xml:space="preserve">2035-06-12</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -25091,30 +25091,30 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herredsvej 45</t>
+          <t xml:space="preserve">Brostræde 3</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t xml:space="preserve">6580</t>
+          <t xml:space="preserve">6000</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">9071031</t>
+          <t xml:space="preserve">8761653</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J335">
-        <v>2017</v>
+        <v>1713</v>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t xml:space="preserve">311826644</t>
+          <t xml:space="preserve">311839054</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
@@ -25124,7 +25124,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-23</t>
+          <t xml:space="preserve">2035-06-18</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -25166,30 +25166,30 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herredsvej 45</t>
+          <t xml:space="preserve">Brostræde 3A</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t xml:space="preserve">6580</t>
+          <t xml:space="preserve">6000</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">9071031</t>
+          <t xml:space="preserve">8761653</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J336">
-        <v>803</v>
+        <v>4121</v>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t xml:space="preserve">311826644</t>
+          <t xml:space="preserve">311839051</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
@@ -25199,7 +25199,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-23</t>
+          <t xml:space="preserve">2035-06-18</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -25241,30 +25241,30 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herredsvej 45B</t>
+          <t xml:space="preserve">Birkevej 24</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t xml:space="preserve">6580</t>
+          <t xml:space="preserve">6070</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">9071031</t>
+          <t xml:space="preserve">304880, 304881</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J337">
-        <v>371</v>
+        <v>2656</v>
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t xml:space="preserve">311826639</t>
+          <t xml:space="preserve">311841720</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
@@ -25274,7 +25274,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-23</t>
+          <t xml:space="preserve">2035-06-30</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -25316,17 +25316,17 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sjølund Gade 28</t>
+          <t xml:space="preserve">Bredgade 1</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t xml:space="preserve">6093</t>
+          <t xml:space="preserve">6000</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">5069465</t>
+          <t xml:space="preserve">5675450</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -25335,21 +25335,21 @@
         </is>
       </c>
       <c r="J338">
-        <v>1387</v>
+        <v>2112</v>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t xml:space="preserve">311827156</t>
+          <t xml:space="preserve">311844296</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-25</t>
+          <t xml:space="preserve">2035-07-11</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -25391,30 +25391,30 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjarupvej 10</t>
+          <t xml:space="preserve">Kongensgade 34A</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t xml:space="preserve">6000</t>
+          <t xml:space="preserve">6070</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t xml:space="preserve">5069995</t>
+          <t xml:space="preserve">5766969</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J339">
-        <v>5886</v>
+        <v>2092</v>
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t xml:space="preserve">311828899</t>
+          <t xml:space="preserve">311847624</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-02</t>
+          <t xml:space="preserve">2035-08-06</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -25466,17 +25466,17 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkevej 9A</t>
+          <t xml:space="preserve">Ved Padholm 2</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t xml:space="preserve">6070</t>
+          <t xml:space="preserve">6000</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">5170804</t>
+          <t xml:space="preserve">100497241</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -25485,21 +25485,21 @@
         </is>
       </c>
       <c r="J340">
-        <v>361</v>
+        <v>1865</v>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t xml:space="preserve">311832714</t>
+          <t xml:space="preserve">311861662</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-19</t>
+          <t xml:space="preserve">2035-10-13</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -25541,40 +25541,40 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkevej 9A</t>
+          <t xml:space="preserve">Kobbervej 14</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t xml:space="preserve">6070</t>
+          <t xml:space="preserve">6000</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">5170804</t>
+          <t xml:space="preserve">100643290</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J341">
-        <v>525</v>
+        <v>711</v>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t xml:space="preserve">311832714</t>
+          <t xml:space="preserve">311869504</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve">Ingeniørgruppen Haderslev ApS</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-19</t>
+          <t xml:space="preserve">2035-11-20</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -25616,7 +25616,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ågade 27</t>
+          <t xml:space="preserve">Kobbervej 14</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
@@ -25626,30 +25626,30 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">9218207</t>
+          <t xml:space="preserve">100643290</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J342">
-        <v>5961</v>
+        <v>307</v>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t xml:space="preserve">311832620</t>
+          <t xml:space="preserve">311869505</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve">Ingeniørgruppen Haderslev ApS</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-19</t>
+          <t xml:space="preserve">2035-11-20</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -25691,40 +25691,40 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 1A</t>
+          <t xml:space="preserve">Stadionvej 11</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t xml:space="preserve">6580</t>
+          <t xml:space="preserve">6000</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t xml:space="preserve">5028587</t>
+          <t xml:space="preserve">100891244, 100891245</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="J343">
-        <v>3079</v>
+        <v>5997</v>
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t xml:space="preserve">311833037</t>
+          <t xml:space="preserve">311871668</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve">Højbjerg Energimærkning</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-20</t>
+          <t xml:space="preserve">2035-12-04</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -25766,7 +25766,7 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rytterskolevej 15</t>
+          <t xml:space="preserve">Brændkjærgade 92</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
@@ -25776,30 +25776,30 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">10170544</t>
+          <t xml:space="preserve">7841251</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J344">
-        <v>636</v>
+        <v>1613</v>
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t xml:space="preserve">311834137</t>
+          <t xml:space="preserve">311929645</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-25</t>
+          <t xml:space="preserve">2036-10-02</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -25841,7 +25841,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seestvej 10</t>
+          <t xml:space="preserve">Brændkjærgade 92</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
@@ -25851,30 +25851,30 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t xml:space="preserve">100068900</t>
+          <t xml:space="preserve">7841251</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J345">
-        <v>1983</v>
+        <v>486</v>
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t xml:space="preserve">311837586</t>
+          <t xml:space="preserve">311929645</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-12</t>
+          <t xml:space="preserve">2036-10-02</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -25916,7 +25916,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brostræde 3</t>
+          <t xml:space="preserve">Brændkjærgade 92</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
@@ -25926,30 +25926,30 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">8761653</t>
+          <t xml:space="preserve">7841251</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J346">
-        <v>1713</v>
+        <v>540</v>
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t xml:space="preserve">311839054</t>
+          <t xml:space="preserve">311929645</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-18</t>
+          <t xml:space="preserve">2036-10-02</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -25991,7 +25991,7 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brostræde 3A</t>
+          <t xml:space="preserve">Brændkjærgade 92</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
@@ -26001,30 +26001,30 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t xml:space="preserve">8761653</t>
+          <t xml:space="preserve">7841251</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J347">
-        <v>4121</v>
+        <v>428</v>
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t xml:space="preserve">311839051</t>
+          <t xml:space="preserve">311929645</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-18</t>
+          <t xml:space="preserve">2036-10-02</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -26066,40 +26066,40 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkevej 24</t>
+          <t xml:space="preserve">Brændkjærgade 92</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t xml:space="preserve">6070</t>
+          <t xml:space="preserve">6000</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t xml:space="preserve">304880, 304881</t>
+          <t xml:space="preserve">7841251</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J348">
-        <v>2656</v>
+        <v>2260</v>
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t xml:space="preserve">311841720</t>
+          <t xml:space="preserve">311929645</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-30</t>
+          <t xml:space="preserve">2036-10-02</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -26141,7 +26141,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 1</t>
+          <t xml:space="preserve">Brændkjærgade 92</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
@@ -26151,30 +26151,30 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t xml:space="preserve">5675450</t>
+          <t xml:space="preserve">7841251</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J349">
-        <v>2112</v>
+        <v>1303</v>
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t xml:space="preserve">311844296</t>
+          <t xml:space="preserve">311929645</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-11</t>
+          <t xml:space="preserve">2036-10-02</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -26216,40 +26216,40 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongensgade 34A</t>
+          <t xml:space="preserve">Brændkjærgade 92</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t xml:space="preserve">6070</t>
+          <t xml:space="preserve">6000</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t xml:space="preserve">5766969</t>
+          <t xml:space="preserve">7841251</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="J350">
-        <v>2092</v>
+        <v>253</v>
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t xml:space="preserve">311847624</t>
+          <t xml:space="preserve">311929645</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-06</t>
+          <t xml:space="preserve">2036-10-02</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -26291,7 +26291,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Padholm 2</t>
+          <t xml:space="preserve">Brændkjærgade 92</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
@@ -26301,30 +26301,30 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t xml:space="preserve">100497241</t>
+          <t xml:space="preserve">7841251</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J351">
-        <v>1865</v>
+        <v>562</v>
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t xml:space="preserve">311861662</t>
+          <t xml:space="preserve">311929645</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-13</t>
+          <t xml:space="preserve">2036-10-02</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -26366,7 +26366,7 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kobbervej 14</t>
+          <t xml:space="preserve">Brændkjærgade 92</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
@@ -26376,30 +26376,30 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t xml:space="preserve">100643290</t>
+          <t xml:space="preserve">7841251</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J352">
-        <v>711</v>
+        <v>505</v>
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t xml:space="preserve">311869504</t>
+          <t xml:space="preserve">311929645</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingeniørgruppen Haderslev ApS</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-20</t>
+          <t xml:space="preserve">2036-10-02</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -26441,7 +26441,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kobbervej 14</t>
+          <t xml:space="preserve">Brændkjærgade 92</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
@@ -26451,30 +26451,30 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t xml:space="preserve">100643290</t>
+          <t xml:space="preserve">7841251</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J353">
-        <v>307</v>
+        <v>380</v>
       </c>
       <c r="K353" t="inlineStr">
         <is>
-          <t xml:space="preserve">311869505</t>
+          <t xml:space="preserve">311929645</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingeniørgruppen Haderslev ApS</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-20</t>
+          <t xml:space="preserve">2036-10-02</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -26516,7 +26516,7 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 11</t>
+          <t xml:space="preserve">Dannersvej 4</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
@@ -26526,30 +26526,30 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t xml:space="preserve">100891244, 100891245</t>
+          <t xml:space="preserve">7841251</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J354">
-        <v>5997</v>
+        <v>2917</v>
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871668</t>
+          <t xml:space="preserve">311929645</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højbjerg Energimærkning</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-04</t>
+          <t xml:space="preserve">2036-10-02</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
